--- a/results/Int All Data -0.5/Rando_5_permute.xlsx
+++ b/results/Int All Data -0.5/Rando_5_permute.xlsx
@@ -440,1547 +440,1547 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.8264257057456701</v>
+        <v>0.8103175833347225</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>hrv_iqr</t>
+          <t>accy_sum</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.8269522505934935</v>
+        <v>0.8204247970168725</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>hrv_rms</t>
+          <t>accy_kurtosis</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.8289176160376091</v>
+        <v>0.8196528031729603</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>scl_pct_95</t>
+          <t>accy_rms</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.831549630886564</v>
+        <v>0.8254433777186935</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>accz_pct_95</t>
+          <t>hrv_sum</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.8183537324386032</v>
+        <v>0.8284614781633747</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>accz_ptp</t>
+          <t>accz_rms</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.8170202562813839</v>
+        <v>0.8261802567495814</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>accy_iqr</t>
+          <t>accx_sum</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.8211966135132441</v>
+        <v>0.8259348077534926</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>hrv_svd_entropy</t>
+          <t>hrv_rms</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.8176168534077153</v>
+        <v>0.8294092234199486</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>accx_svd_entropy</t>
+          <t>bvp_energy</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.8176870830337638</v>
+        <v>0.825373502787726</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>hrv_kurtosis</t>
+          <t>bvp_lineintegral</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.8167395151247303</v>
+        <v>0.825022532005024</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>scr_pct_95</t>
+          <t>scl_iqr</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.8154760912460191</v>
+        <v>0.8264964674143402</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>scr_iqr</t>
+          <t>accz_n_sign_changes</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.8173009974380374</v>
+        <v>0.8230924587214732</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>hrv_perm_entropy</t>
+          <t>accz_pct_5</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.8163534295290039</v>
+        <v>0.8230571665609083</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>scr_svd_entropy</t>
+          <t>accy_energy</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.8175466237816668</v>
+        <v>0.833655278235236</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>hrv_n_below_mean</t>
+          <t>accz_perm_entropy</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.8159322291202533</v>
+        <v>0.8280404551021646</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>scr_entropy</t>
+          <t>scr_skewness</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.8159322291202533</v>
+        <v>0.8280404551021646</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
         <is>
-          <t>scr_perm_entropy</t>
+          <t>accy_entropy</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.8150548908372683</v>
+        <v>0.8280404551021646</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>accz_max</t>
+          <t>scr_pct_5</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.8100010179748827</v>
+        <v>0.8264260604407512</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="inlineStr">
         <is>
-          <t>scr_ptp</t>
+          <t>bvp_n_below_mean</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.8145281686419045</v>
+        <v>0.8306025950201521</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="inlineStr">
         <is>
-          <t>accx_std</t>
+          <t>accy_perm_entropy</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.8210205074055013</v>
+        <v>0.8354454243093111</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="inlineStr">
         <is>
-          <t>accx_ptp</t>
+          <t>scl_pct_5</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.8209855699400175</v>
+        <v>0.8361823033401991</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="inlineStr">
         <is>
-          <t>accx_n_below_mean</t>
+          <t>accx_rms</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.8172657052774727</v>
+        <v>0.8203205166630428</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>accy_svd_entropy</t>
+          <t>bvp_skewness</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.8205294320657832</v>
+        <v>0.8224261640117149</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
         <is>
-          <t>bvp_n_above_mean</t>
+          <t>scr_kurtosis</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.8202834510270729</v>
+        <v>0.8222507672941342</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="inlineStr">
         <is>
-          <t>hrv_energy</t>
+          <t>accx_pct_95</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.8269866560163557</v>
+        <v>0.8265674064305508</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="1" t="inlineStr">
         <is>
-          <t>accx_peaks</t>
+          <t>accx_pct_5</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.8293028148956327</v>
+        <v>0.8183915074647354</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="1" t="inlineStr">
         <is>
-          <t>hrv_std</t>
+          <t>accx_energy</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0.831303472500313</v>
+        <v>0.8091274039902487</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="1" t="inlineStr">
         <is>
-          <t>accy_entropy</t>
+          <t>accx_n_below_mean</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0.8316193284699909</v>
+        <v>0.8062501174927457</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="1" t="inlineStr">
         <is>
-          <t>accz_n_below_mean</t>
+          <t>hrv_iqr_5_95</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>0.8330581490662829</v>
+        <v>0.7921435394241809</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="1" t="inlineStr">
         <is>
-          <t>scl_svd_entropy</t>
+          <t>bvp_min</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>0.8283552469865993</v>
+        <v>0.7990221411310445</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="1" t="inlineStr">
         <is>
-          <t>scl_pct_5</t>
+          <t>accz_kurtosis</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>0.8353033689293493</v>
+        <v>0.8014785819148782</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="1" t="inlineStr">
         <is>
-          <t>hrv_iqr_5_95</t>
+          <t>scr_max</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>0.8441122212673042</v>
+        <v>0.8006014209794337</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="1" t="inlineStr">
         <is>
-          <t>scl_mean</t>
+          <t>bvp_n_above_mean</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>0.8482534636861403</v>
+        <v>0.803970137511736</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="1" t="inlineStr">
         <is>
-          <t>bvp_pct_95</t>
+          <t>scr_perm_entropy</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>0.8428138599231092</v>
+        <v>0.8039350226987116</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="1" t="inlineStr">
         <is>
-          <t>scl_min</t>
+          <t>scr_svd_entropy</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>0.8443578476109335</v>
+        <v>0.8039703148592765</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="1" t="inlineStr">
         <is>
-          <t>scr_skewness</t>
+          <t>accx_svd_entropy</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>0.8440419916412557</v>
+        <v>0.7961797920990252</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="1" t="inlineStr">
         <is>
-          <t>bvp_std</t>
+          <t>scl_pct_95</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>0.8415151438838331</v>
+        <v>0.8005311913533852</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="1" t="inlineStr">
         <is>
-          <t>scl_sum</t>
+          <t>accy_iqr</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>0.8354085360208816</v>
+        <v>0.8246043465044622</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="1" t="inlineStr">
         <is>
-          <t>accz_kurtosis</t>
+          <t>accy_min</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>0.8344609681118482</v>
+        <v>0.8189536991682045</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="1" t="inlineStr">
         <is>
-          <t>accx_min</t>
+          <t>accz_ptp</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>0.8350575652381795</v>
+        <v>0.8129178529739232</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="1" t="inlineStr">
         <is>
-          <t>accz_iqr</t>
+          <t>scr_sum</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>0.8366017302735445</v>
+        <v>0.8123563706606161</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="1" t="inlineStr">
         <is>
-          <t>scr_min</t>
+          <t>bvp_ptp</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>0.8366017302735445</v>
+        <v>0.8183922168548974</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="1" t="inlineStr">
         <is>
-          <t>accz_mean</t>
+          <t>accz_iqr_5_95</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>0.8044542962973735</v>
+        <v>0.7956177777430964</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="1" t="inlineStr">
         <is>
-          <t>accy_n_above_mean</t>
+          <t>accy_pct_5</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>0.8057528349891091</v>
+        <v>0.8092689273275889</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="1" t="inlineStr">
         <is>
-          <t>accy_pct_5</t>
+          <t>accx_lineintegral</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>0.8037874695449936</v>
+        <v>0.8169186361406622</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="1" t="inlineStr">
         <is>
-          <t>scl_kurtosis</t>
+          <t>accx_mean</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>0.8034716135753157</v>
+        <v>0.8266748790401099</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="1" t="inlineStr">
         <is>
-          <t>bvp_perm_entropy</t>
+          <t>bvp_max</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>0.8093327724421785</v>
+        <v>0.8431336175386785</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="1" t="inlineStr">
         <is>
-          <t>scr_rms</t>
+          <t>accz_entropy</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>0.8071217806544337</v>
+        <v>0.8406420619418208</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="1" t="inlineStr">
         <is>
-          <t>accy_ptp</t>
+          <t>scr_std</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>0.8211950173853795</v>
+        <v>0.8376941911231881</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="1" t="inlineStr">
         <is>
-          <t>accy_lineintegral</t>
+          <t>accz_max</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>0.8236867503297778</v>
+        <v>0.8320078969312845</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="1" t="inlineStr">
         <is>
-          <t>scl_ptp</t>
+          <t>accx_max</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>0.8253011449911911</v>
+        <v>0.8339030327493515</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="1" t="inlineStr">
         <is>
-          <t>accy_rms</t>
+          <t>bvp_n_sign_changes</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>0.8258624499569578</v>
+        <v>0.8289550363686602</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="1" t="inlineStr">
         <is>
-          <t>accx_sum</t>
+          <t>scl_rms</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>0.8295828466621242</v>
+        <v>0.8281481050592643</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="1" t="inlineStr">
         <is>
-          <t>bvp_ptp</t>
+          <t>accy_peaks</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>0.8293022828530112</v>
+        <v>0.8220072691209911</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="1" t="inlineStr">
         <is>
-          <t>bvp_mean</t>
+          <t>accz_n_below_mean</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>0.8287056857266798</v>
+        <v>0.8122508488740028</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="1" t="inlineStr">
         <is>
-          <t>scl_rms</t>
+          <t>accx_peaks</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>0.8300042244184154</v>
+        <v>0.8081798360812152</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="1" t="inlineStr">
         <is>
-          <t>accz_n_above_mean</t>
+          <t>bvp_perm_entropy</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>0.8181423341702956</v>
+        <v>0.7788084231569068</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="1" t="inlineStr">
         <is>
-          <t>bvp_max</t>
+          <t>accy_max</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>0.822072887710986</v>
+        <v>0.6907975780001085</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="1" t="inlineStr">
         <is>
-          <t>scr_pct_5</t>
+          <t>hrv_lineintegral</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>0.8062447970665299</v>
+        <v>0.672444058378554</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="1" t="inlineStr">
         <is>
-          <t>accx_pct_5</t>
+          <t>accy_n_below_mean</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>0.7909787207780024</v>
+        <v>0.6523009247255458</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="1" t="inlineStr">
         <is>
-          <t>bvp_skewness</t>
+          <t>accy_lineintegral</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>0.7838894301929932</v>
+        <v>0.6777781403549717</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="1" t="inlineStr">
         <is>
-          <t>scl_skewness</t>
+          <t>accx_perm_entropy</t>
         </is>
       </c>
       <c r="B63" t="n">
-        <v>0.7838894301929932</v>
+        <v>0.6308947218889074</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="1" t="inlineStr">
         <is>
-          <t>bvp_svd_entropy</t>
+          <t>scl_mean</t>
         </is>
       </c>
       <c r="B64" t="n">
-        <v>0.7764491688252818</v>
+        <v>0.6413172594981136</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="1" t="inlineStr">
         <is>
-          <t>scl_n_below_mean</t>
+          <t>accx_skewness</t>
         </is>
       </c>
       <c r="B65" t="n">
-        <v>0.7770457659516132</v>
+        <v>0.6390362154318607</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="1" t="inlineStr">
         <is>
-          <t>scr_energy</t>
+          <t>hrv_min</t>
         </is>
       </c>
       <c r="B66" t="n">
-        <v>0.7671841786130926</v>
+        <v>0.6158045743605823</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="1" t="inlineStr">
         <is>
-          <t>scl_max</t>
+          <t>accz_std</t>
         </is>
       </c>
       <c r="B67" t="n">
-        <v>0.7640958485423628</v>
+        <v>0.6729693617935937</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="1" t="inlineStr">
         <is>
-          <t>bvp_energy</t>
+          <t>accz_energy</t>
         </is>
       </c>
       <c r="B68" t="n">
-        <v>0.7521988434812188</v>
+        <v>0.6682318769435074</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="1" t="inlineStr">
         <is>
-          <t>accy_pct_95</t>
+          <t>accx_iqr_5_95</t>
         </is>
       </c>
       <c r="B69" t="n">
-        <v>0.7925936474820374</v>
+        <v>0.6912175369760755</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="1" t="inlineStr">
         <is>
-          <t>bvp_iqr_5_95</t>
+          <t>bvp_kurtosis</t>
         </is>
       </c>
       <c r="B70" t="n">
-        <v>0.7878206931238456</v>
+        <v>0.6794615232096499</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="1" t="inlineStr">
         <is>
-          <t>accy_energy</t>
+          <t>hrv_peaks</t>
         </is>
       </c>
       <c r="B71" t="n">
-        <v>0.837269798458708</v>
+        <v>0.676127566795291</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="1" t="inlineStr">
         <is>
-          <t>bvp_rms</t>
+          <t>accx_n_above_mean</t>
         </is>
       </c>
       <c r="B72" t="n">
-        <v>0.825056582732805</v>
+        <v>0.6793561787705772</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="1" t="inlineStr">
         <is>
-          <t>scl_iqr_5_95</t>
+          <t>bvp_iqr</t>
         </is>
       </c>
       <c r="B73" t="n">
-        <v>0.8249163008282485</v>
+        <v>0.6843742274297766</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="1" t="inlineStr">
         <is>
-          <t>accx_iqr</t>
+          <t>hrv_skewness</t>
         </is>
       </c>
       <c r="B74" t="n">
-        <v>0.8291981798467221</v>
+        <v>0.6767943935476708</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="1" t="inlineStr">
         <is>
-          <t>hrv_pct_5</t>
+          <t>scr_n_above_mean</t>
         </is>
       </c>
       <c r="B75" t="n">
-        <v>0.8301109876378123</v>
+        <v>0.6790053853354157</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="1" t="inlineStr">
         <is>
-          <t>accz_rms</t>
+          <t>bvp_peaks</t>
         </is>
       </c>
       <c r="B76" t="n">
-        <v>0.838428409940968</v>
+        <v>0.6676711040203623</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="1" t="inlineStr">
         <is>
-          <t>hrv_pct_95</t>
+          <t>scl_lineintegral</t>
         </is>
       </c>
       <c r="B77" t="n">
-        <v>0.8383230655018953</v>
+        <v>0.6709346534611323</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="1" t="inlineStr">
         <is>
-          <t>accz_lineintegral</t>
+          <t>scr_rms</t>
         </is>
       </c>
       <c r="B78" t="n">
-        <v>0.8231268641443353</v>
+        <v>0.6745842884976287</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="1" t="inlineStr">
         <is>
-          <t>accx_mean</t>
+          <t>scl_peaks</t>
         </is>
       </c>
       <c r="B79" t="n">
-        <v>0.8131251722487987</v>
+        <v>0.6745842884976287</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="1" t="inlineStr">
         <is>
-          <t>accy_std</t>
+          <t>scl_n_sign_changes</t>
         </is>
       </c>
       <c r="B80" t="n">
-        <v>0.8058251927856439</v>
+        <v>0.6745842884976287</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="1" t="inlineStr">
         <is>
-          <t>hrv_n_sign_changes</t>
+          <t>scl_ptp</t>
         </is>
       </c>
       <c r="B81" t="n">
-        <v>0.8058251927856439</v>
+        <v>0.6699869082045584</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="1" t="inlineStr">
         <is>
-          <t>hrv_mean</t>
+          <t>hrv_max</t>
         </is>
       </c>
       <c r="B82" t="n">
-        <v>0.8016137207407594</v>
+        <v>0.6655305192062065</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="1" t="inlineStr">
         <is>
-          <t>accy_perm_entropy</t>
+          <t>scl_sum</t>
         </is>
       </c>
       <c r="B83" t="n">
-        <v>0.790876213899578</v>
+        <v>0.6514237637901015</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="1" t="inlineStr">
         <is>
-          <t>accz_n_sign_changes</t>
+          <t>scl_entropy</t>
         </is>
       </c>
       <c r="B84" t="n">
-        <v>0.7837878100522715</v>
+        <v>0.6591089421112799</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="1" t="inlineStr">
         <is>
-          <t>accx_skewness</t>
+          <t>bvp_iqr_5_95</t>
         </is>
       </c>
       <c r="B85" t="n">
-        <v>0.7812957224127921</v>
+        <v>0.631736590663787</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="1" t="inlineStr">
         <is>
-          <t>bvp_entropy</t>
+          <t>scl_perm_entropy</t>
         </is>
       </c>
       <c r="B86" t="n">
-        <v>0.7812957224127921</v>
+        <v>0.6306136260371727</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="1" t="inlineStr">
         <is>
-          <t>accx_entropy</t>
+          <t>bvp_rms</t>
         </is>
       </c>
       <c r="B87" t="n">
-        <v>0.7781724548765785</v>
+        <v>0.6135231755992485</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="1" t="inlineStr">
         <is>
-          <t>accx_iqr_5_95</t>
+          <t>hrv_n_above_mean</t>
         </is>
       </c>
       <c r="B88" t="n">
-        <v>0.7686964210911627</v>
+        <v>0.6135231755992485</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="1" t="inlineStr">
         <is>
-          <t>bvp_min</t>
+          <t>scl_std</t>
         </is>
       </c>
       <c r="B89" t="n">
-        <v>0.7535002197336027</v>
+        <v>0.6041870690233081</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="1" t="inlineStr">
         <is>
-          <t>accz_min</t>
+          <t>scl_min</t>
         </is>
       </c>
       <c r="B90" t="n">
-        <v>0.7000891703433767</v>
+        <v>0.6268574051288199</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="1" t="inlineStr">
         <is>
-          <t>scr_iqr_5_95</t>
+          <t>scr_mean</t>
         </is>
       </c>
       <c r="B91" t="n">
-        <v>0.6833145758751303</v>
+        <v>0.6272429586819247</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="1" t="inlineStr">
         <is>
-          <t>bvp_pct_5</t>
+          <t>accy_skewness</t>
         </is>
       </c>
       <c r="B92" t="n">
-        <v>0.6415910841006867</v>
+        <v>0.6248565701765991</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="1" t="inlineStr">
         <is>
-          <t>accy_n_below_mean</t>
+          <t>scr_entropy</t>
         </is>
       </c>
       <c r="B93" t="n">
-        <v>0.6043241586721351</v>
+        <v>0.6228913820800241</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="1" t="inlineStr">
         <is>
-          <t>accz_perm_entropy</t>
+          <t>accz_skewness</t>
         </is>
       </c>
       <c r="B94" t="n">
-        <v>0.5296808843825274</v>
+        <v>0.6146800136061032</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="1" t="inlineStr">
         <is>
-          <t>accy_iqr_5_95</t>
+          <t>bvp_std</t>
         </is>
       </c>
       <c r="B95" t="n">
-        <v>0.6038611042438202</v>
+        <v>0.5889899809280454</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="1" t="inlineStr">
         <is>
-          <t>scl_n_above_mean</t>
+          <t>scl_skewness</t>
         </is>
       </c>
       <c r="B96" t="n">
-        <v>0.6043172421180546</v>
+        <v>0.5889899809280454</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="1" t="inlineStr">
         <is>
-          <t>scl_energy</t>
+          <t>bvp_sum</t>
         </is>
       </c>
       <c r="B97" t="n">
-        <v>0.6063875973061619</v>
+        <v>0.5889899809280454</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="1" t="inlineStr">
         <is>
-          <t>accy_mean</t>
+          <t>scl_max</t>
         </is>
       </c>
       <c r="B98" t="n">
-        <v>0.569048491428616</v>
+        <v>0.5988159214109203</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="1" t="inlineStr">
         <is>
-          <t>bvp_sum</t>
+          <t>accz_peaks</t>
         </is>
       </c>
       <c r="B99" t="n">
-        <v>0.569048491428616</v>
+        <v>0.5710537600693499</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="1" t="inlineStr">
         <is>
-          <t>scr_n_above_mean</t>
+          <t>scr_ptp</t>
         </is>
       </c>
       <c r="B100" t="n">
-        <v>0.5668016754376848</v>
+        <v>0.5718952741491485</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="1" t="inlineStr">
         <is>
-          <t>accy_peaks</t>
+          <t>accz_min</t>
         </is>
       </c>
       <c r="B101" t="n">
-        <v>0.5863102595906889</v>
+        <v>0.554526210725057</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="1" t="inlineStr">
         <is>
-          <t>bvp_n_sign_changes</t>
+          <t>accz_svd_entropy</t>
         </is>
       </c>
       <c r="B102" t="n">
-        <v>0.5859229325621789</v>
+        <v>0.5772327257288363</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="1" t="inlineStr">
         <is>
-          <t>accy_n_sign_changes</t>
+          <t>accy_n_above_mean</t>
         </is>
       </c>
       <c r="B103" t="n">
-        <v>0.5909406265262973</v>
+        <v>0.6175888679658201</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="1" t="inlineStr">
         <is>
-          <t>hrv_ptp</t>
+          <t>accy_svd_entropy</t>
         </is>
       </c>
       <c r="B104" t="n">
-        <v>0.6088396044014822</v>
+        <v>0.5939709639512748</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="1" t="inlineStr">
         <is>
-          <t>accx_pct_95</t>
+          <t>accx_entropy</t>
         </is>
       </c>
       <c r="B105" t="n">
-        <v>0.6412323100262014</v>
+        <v>0.6024283134639061</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="1" t="inlineStr">
         <is>
-          <t>scl_iqr</t>
+          <t>hrv_perm_entropy</t>
         </is>
       </c>
       <c r="B106" t="n">
-        <v>0.6097853988351104</v>
+        <v>0.5994802652977328</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="1" t="inlineStr">
         <is>
-          <t>accy_max</t>
+          <t>accy_std</t>
         </is>
       </c>
       <c r="B107" t="n">
-        <v>0.6355117877589762</v>
+        <v>0.6335891630721275</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="1" t="inlineStr">
         <is>
-          <t>accx_max</t>
+          <t>accx_iqr</t>
         </is>
       </c>
       <c r="B108" t="n">
-        <v>0.649689482191292</v>
+        <v>0.6311325449407534</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="1" t="inlineStr">
         <is>
-          <t>hrv_sum</t>
+          <t>scl_svd_entropy</t>
         </is>
       </c>
       <c r="B109" t="n">
-        <v>0.6501110372951238</v>
+        <v>0.6260089744949409</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="1" t="inlineStr">
         <is>
-          <t>scl_n_sign_changes</t>
+          <t>scr_pct_95</t>
         </is>
       </c>
       <c r="B110" t="n">
-        <v>0.6501110372951238</v>
+        <v>0.6180411041941629</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="1" t="inlineStr">
         <is>
-          <t>scr_n_below_mean</t>
+          <t>accy_pct_95</t>
         </is>
       </c>
       <c r="B111" t="n">
-        <v>0.6501110372951238</v>
+        <v>0.4690778601813272</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="1" t="inlineStr">
         <is>
-          <t>accx_n_sign_changes</t>
+          <t>scr_iqr_5_95</t>
         </is>
       </c>
       <c r="B112" t="n">
-        <v>0.6500055155085103</v>
+        <v>0.4527941637052583</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="1" t="inlineStr">
         <is>
-          <t>accy_sum</t>
+          <t>bvp_svd_entropy</t>
         </is>
       </c>
       <c r="B113" t="n">
-        <v>0.6581118942384395</v>
+        <v>0.4545486629236877</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="1" t="inlineStr">
         <is>
-          <t>scl_std</t>
+          <t>accy_mean</t>
         </is>
       </c>
       <c r="B114" t="n">
-        <v>0.5738108049343761</v>
+        <v>0.441353119170808</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="1" t="inlineStr">
         <is>
-          <t>accz_sum</t>
+          <t>scl_kurtosis</t>
         </is>
       </c>
       <c r="B115" t="n">
-        <v>0.5148113571946172</v>
+        <v>0.441353119170808</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="1" t="inlineStr">
         <is>
-          <t>scr_n_sign_changes</t>
+          <t>hrv_n_below_mean</t>
         </is>
       </c>
       <c r="B116" t="n">
-        <v>0.5148113571946172</v>
+        <v>0.4419848311101637</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="1" t="inlineStr">
         <is>
-          <t>accy_skewness</t>
+          <t>scl_n_above_mean</t>
         </is>
       </c>
       <c r="B117" t="n">
-        <v>0.5144598543692936</v>
+        <v>0.4417040899535101</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="1" t="inlineStr">
         <is>
-          <t>accy_min</t>
+          <t>scl_n_below_mean</t>
         </is>
       </c>
       <c r="B118" t="n">
-        <v>0.5210575375719632</v>
+        <v>0.4441605307373437</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="1" t="inlineStr">
         <is>
-          <t>scl_perm_entropy</t>
+          <t>accy_iqr_5_95</t>
         </is>
       </c>
       <c r="B119" t="n">
-        <v>0.5210575375719632</v>
+        <v>0.4866207241951348</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="1" t="inlineStr">
         <is>
-          <t>bvp_lineintegral</t>
+          <t>bvp_pct_5</t>
         </is>
       </c>
       <c r="B120" t="n">
-        <v>0.5070195930015823</v>
+        <v>0.4674934372542628</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="1" t="inlineStr">
         <is>
-          <t>accz_std</t>
+          <t>accz_n_above_mean</t>
         </is>
       </c>
       <c r="B121" t="n">
-        <v>0.4910521071902723</v>
+        <v>0.4505719990224604</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" s="1" t="inlineStr">
         <is>
-          <t>accz_energy</t>
+          <t>accz_sum</t>
         </is>
       </c>
       <c r="B122" t="n">
-        <v>0.4887363030060763</v>
+        <v>0.4537647867945602</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" s="1" t="inlineStr">
         <is>
-          <t>scr_std</t>
+          <t>accz_lineintegral</t>
         </is>
       </c>
       <c r="B123" t="n">
-        <v>0.4857882548399031</v>
+        <v>0.4766000561127618</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" s="1" t="inlineStr">
         <is>
-          <t>accz_peaks</t>
+          <t>scr_energy</t>
         </is>
       </c>
       <c r="B124" t="n">
-        <v>0.4950871184323329</v>
+        <v>0.480178929480588</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" s="1" t="inlineStr">
         <is>
-          <t>accx_n_above_mean</t>
+          <t>scr_peaks</t>
         </is>
       </c>
       <c r="B125" t="n">
-        <v>0.4943151245884207</v>
+        <v>0.480178929480588</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" s="1" t="inlineStr">
         <is>
-          <t>hrv_min</t>
+          <t>hrv_kurtosis</t>
         </is>
       </c>
       <c r="B126" t="n">
-        <v>0.4941046130578157</v>
+        <v>0.4795823323542567</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" s="1" t="inlineStr">
         <is>
-          <t>scr_lineintegral</t>
+          <t>hrv_pct_95</t>
         </is>
       </c>
       <c r="B127" t="n">
-        <v>0.4981754485030626</v>
+        <v>0.4812320191762349</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" s="1" t="inlineStr">
         <is>
-          <t>hrv_entropy</t>
+          <t>accy_ptp</t>
         </is>
       </c>
       <c r="B128" t="n">
-        <v>0.497964759624917</v>
+        <v>0.4668076343150466</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" s="1" t="inlineStr">
         <is>
-          <t>accx_lineintegral</t>
+          <t>accx_ptp</t>
         </is>
       </c>
       <c r="B129" t="n">
-        <v>0.4916832870870064</v>
+        <v>0.4898968653112822</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" s="1" t="inlineStr">
         <is>
-          <t>accz_svd_entropy</t>
+          <t>accx_std</t>
         </is>
       </c>
       <c r="B130" t="n">
-        <v>0.4942450723099127</v>
+        <v>0.4828788684375646</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" s="1" t="inlineStr">
         <is>
-          <t>scr_sum</t>
+          <t>accy_n_sign_changes</t>
         </is>
       </c>
       <c r="B131" t="n">
-        <v>0.4932975044008792</v>
+        <v>0.4824934922320003</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" s="1" t="inlineStr">
         <is>
-          <t>bvp_iqr</t>
+          <t>hrv_iqr</t>
         </is>
       </c>
       <c r="B132" t="n">
-        <v>0.4965610538416492</v>
+        <v>0.4737557562577966</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" s="1" t="inlineStr">
         <is>
-          <t>hrv_peaks</t>
+          <t>bvp_entropy</t>
         </is>
       </c>
       <c r="B133" t="n">
-        <v>0.4971927657810049</v>
+        <v>0.4737557562577966</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" s="1" t="inlineStr">
         <is>
-          <t>hrv_skewness</t>
+          <t>accz_iqr</t>
         </is>
       </c>
       <c r="B134" t="n">
-        <v>0.4971576509679806</v>
+        <v>0.4860705921244214</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" s="1" t="inlineStr">
         <is>
-          <t>accz_iqr_5_95</t>
+          <t>bvp_mean</t>
         </is>
       </c>
       <c r="B135" t="n">
-        <v>0.4943151245884207</v>
+        <v>0.4860705921244214</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" s="1" t="inlineStr">
         <is>
-          <t>scr_peaks</t>
+          <t>accz_pct_95</t>
         </is>
       </c>
       <c r="B136" t="n">
-        <v>0.4943151245884207</v>
+        <v>0.4865957181919205</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" s="1" t="inlineStr">
         <is>
-          <t>accx_energy</t>
+          <t>scl_iqr_5_95</t>
         </is>
       </c>
       <c r="B137" t="n">
-        <v>0.4868406351453877</v>
+        <v>0.4851219601301447</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" s="1" t="inlineStr">
         <is>
-          <t>bvp_n_below_mean</t>
+          <t>hrv_energy</t>
         </is>
       </c>
       <c r="B138" t="n">
-        <v>0.4864194347366371</v>
+        <v>0.4845601231217565</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" s="1" t="inlineStr">
         <is>
-          <t>accz_skewness</t>
+          <t>hrv_pct_5</t>
         </is>
       </c>
       <c r="B139" t="n">
-        <v>0.4861386935799836</v>
+        <v>0.4879987145850262</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" s="1" t="inlineStr">
         <is>
-          <t>scl_peaks</t>
+          <t>hrv_svd_entropy</t>
         </is>
       </c>
       <c r="B140" t="n">
-        <v>0.4861386935799836</v>
+        <v>0.4891919088376891</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" s="1" t="inlineStr">
         <is>
-          <t>hrv_n_above_mean</t>
+          <t>accx_n_sign_changes</t>
         </is>
       </c>
       <c r="B141" t="n">
-        <v>0.4861386935799836</v>
+        <v>0.4899639026816012</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" s="1" t="inlineStr">
         <is>
-          <t>scr_max</t>
+          <t>hrv_n_sign_changes</t>
         </is>
       </c>
       <c r="B142" t="n">
-        <v>0.4853317622705877</v>
+        <v>0.4899639026816012</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" s="1" t="inlineStr">
         <is>
-          <t>scl_entropy</t>
+          <t>accx_kurtosis</t>
         </is>
       </c>
       <c r="B143" t="n">
-        <v>0.489998840147085</v>
+        <v>0.4899990174946254</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" s="1" t="inlineStr">
         <is>
-          <t>accx_kurtosis</t>
+          <t>hrv_mean</t>
         </is>
       </c>
       <c r="B144" t="n">
-        <v>0.4894022430207535</v>
+        <v>0.4901041845861577</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" s="1" t="inlineStr">
         <is>
-          <t>hrv_lineintegral</t>
+          <t>accx_min</t>
         </is>
       </c>
       <c r="B145" t="n">
-        <v>0.4949117217147521</v>
+        <v>0.4936835899966056</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" s="1" t="inlineStr">
         <is>
-          <t>accx_perm_entropy</t>
+          <t>scl_energy</t>
         </is>
       </c>
       <c r="B146" t="n">
-        <v>0.4998246032824192</v>
+        <v>0.4959646340628583</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" s="1" t="inlineStr">
         <is>
-          <t>scr_kurtosis</t>
+          <t>hrv_ptp</t>
         </is>
       </c>
       <c r="B147" t="n">
-        <v>0.4998246032824192</v>
+        <v>0.4936486525311218</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" s="1" t="inlineStr">
         <is>
-          <t>accz_entropy</t>
+          <t>hrv_entropy</t>
         </is>
       </c>
       <c r="B148" t="n">
-        <v>0.500140459252097</v>
+        <v>0.4927361994351126</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" s="1" t="inlineStr">
         <is>
-          <t>scl_lineintegral</t>
+          <t>scr_n_sign_changes</t>
         </is>
       </c>
       <c r="B149" t="n">
-        <v>0.4992982357821363</v>
+        <v>0.4927361994351126</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" s="1" t="inlineStr">
         <is>
-          <t>bvp_peaks</t>
+          <t>scr_n_below_mean</t>
         </is>
       </c>
       <c r="B150" t="n">
-        <v>0.5000352921605649</v>
+        <v>0.4927361994351126</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" s="1" t="inlineStr">
         <is>
-          <t>scr_mean</t>
+          <t>scr_min</t>
         </is>
       </c>
       <c r="B151" t="n">
-        <v>0.4993686427557254</v>
+        <v>0.4927361994351126</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" s="1" t="inlineStr">
         <is>
-          <t>accy_kurtosis</t>
+          <t>scr_iqr</t>
         </is>
       </c>
       <c r="B152" t="n">
-        <v>0.5002810958517346</v>
+        <v>0.4904551553688599</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" s="1" t="inlineStr">
         <is>
-          <t>accx_rms</t>
+          <t>scr_lineintegral</t>
         </is>
       </c>
       <c r="B153" t="n">
-        <v>0.5007021189129447</v>
+        <v>0.489051449585592</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" s="1" t="inlineStr">
         <is>
-          <t>hrv_max</t>
+          <t>accz_mean</t>
         </is>
       </c>
       <c r="B154" t="n">
-        <v>0.5017548539135105</v>
+        <v>0.5027034859077871</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" s="1" t="inlineStr">
         <is>
-          <t>accz_pct_5</t>
+          <t>hrv_std</t>
         </is>
       </c>
       <c r="B155" t="n">
-        <v>0.4997896658169355</v>
+        <v>0.5022831722367391</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" s="1" t="inlineStr">
         <is>
-          <t>bvp_kurtosis</t>
+          <t>bvp_pct_95</t>
         </is>
       </c>
       <c r="B156" t="n">
-        <v>0.4989823798124585</v>
+        <v>0.4976515638683471</v>
       </c>
     </row>
   </sheetData>
